--- a/sample-data/don-hang-tiktok-shop.xlsx
+++ b/sample-data/don-hang-tiktok-shop.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:H20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,6 +419,9 @@
         <v>unit_price</v>
       </c>
       <c r="G1" t="str">
+        <v>channel</v>
+      </c>
+      <c r="H1" t="str">
         <v>status</v>
       </c>
     </row>
@@ -433,7 +436,7 @@
         <v>Đắc Nhân Tâm - Tái Bản 2025</v>
       </c>
       <c r="D2" t="str">
-        <v>9786045678901</v>
+        <v>9786045678909</v>
       </c>
       <c r="E2" t="str">
         <v>1</v>
@@ -442,6 +445,9 @@
         <v>86.000</v>
       </c>
       <c r="G2" t="str">
+        <v>TikTok Shop</v>
+      </c>
+      <c r="H2" t="str">
         <v>Delivered</v>
       </c>
     </row>
@@ -456,7 +462,7 @@
         <v>Nha Gia Kim</v>
       </c>
       <c r="D3" t="str">
-        <v>9786045678902</v>
+        <v>9786045678916</v>
       </c>
       <c r="E3" t="str">
         <v>2</v>
@@ -465,6 +471,9 @@
         <v>79.000</v>
       </c>
       <c r="G3" t="str">
+        <v>TikTok Shop</v>
+      </c>
+      <c r="H3" t="str">
         <v>Delivered</v>
       </c>
     </row>
@@ -479,7 +488,7 @@
         <v>Ca Phe Cung Tony</v>
       </c>
       <c r="D4" t="str">
-        <v>9786045678904</v>
+        <v>9786045678930</v>
       </c>
       <c r="E4" t="str">
         <v>1</v>
@@ -488,6 +497,9 @@
         <v>72.000</v>
       </c>
       <c r="G4" t="str">
+        <v>TikTok Shop</v>
+      </c>
+      <c r="H4" t="str">
         <v>Delivered</v>
       </c>
     </row>
@@ -511,6 +523,9 @@
         <v>189.000</v>
       </c>
       <c r="G5" t="str">
+        <v>TikTok Shop</v>
+      </c>
+      <c r="H5" t="str">
         <v>Delivered</v>
       </c>
     </row>
@@ -525,7 +540,7 @@
         <v>Atomic Habits</v>
       </c>
       <c r="D6" t="str">
-        <v>9786045678908</v>
+        <v>9786045678978</v>
       </c>
       <c r="E6" t="str">
         <v>1</v>
@@ -534,6 +549,9 @@
         <v>149.000</v>
       </c>
       <c r="G6" t="str">
+        <v>TikTok Shop</v>
+      </c>
+      <c r="H6" t="str">
         <v>Delivered</v>
       </c>
     </row>
@@ -557,6 +575,9 @@
         <v>115.000</v>
       </c>
       <c r="G7" t="str">
+        <v>TikTok Shop</v>
+      </c>
+      <c r="H7" t="str">
         <v>Delivered</v>
       </c>
     </row>
@@ -571,7 +592,7 @@
         <v>Áo Thun Nam Coolmate Cotton</v>
       </c>
       <c r="D8" t="str">
-        <v>8935001234567</v>
+        <v>8935001234562</v>
       </c>
       <c r="E8" t="str">
         <v>1</v>
@@ -580,6 +601,9 @@
         <v>199.000</v>
       </c>
       <c r="G8" t="str">
+        <v>TikTok Shop</v>
+      </c>
+      <c r="H8" t="str">
         <v>Delivered</v>
       </c>
     </row>
@@ -594,7 +618,7 @@
         <v>Quan Jean Slimfit Canifa</v>
       </c>
       <c r="D9" t="str">
-        <v>8935001234568</v>
+        <v>8935001234579</v>
       </c>
       <c r="E9" t="str">
         <v>1</v>
@@ -603,6 +627,9 @@
         <v>449.000</v>
       </c>
       <c r="G9" t="str">
+        <v>TikTok Shop</v>
+      </c>
+      <c r="H9" t="str">
         <v>Delivered</v>
       </c>
     </row>
@@ -617,7 +644,7 @@
         <v>Giày Biti's Hunter Street</v>
       </c>
       <c r="D10" t="str">
-        <v>8935001234569</v>
+        <v>8935001234586</v>
       </c>
       <c r="E10" t="str">
         <v>1</v>
@@ -626,6 +653,9 @@
         <v>850.000</v>
       </c>
       <c r="G10" t="str">
+        <v>TikTok Shop</v>
+      </c>
+      <c r="H10" t="str">
         <v>Delivered</v>
       </c>
     </row>
@@ -640,7 +670,7 @@
         <v>Balo Tomtoc Laptop 15.6"</v>
       </c>
       <c r="D11" t="str">
-        <v>8935001234573</v>
+        <v>8935001234609</v>
       </c>
       <c r="E11" t="str">
         <v>1</v>
@@ -649,6 +679,9 @@
         <v>890.000</v>
       </c>
       <c r="G11" t="str">
+        <v>TikTok Shop</v>
+      </c>
+      <c r="H11" t="str">
         <v>Delivered</v>
       </c>
     </row>
@@ -663,7 +696,7 @@
         <v>Noi Chien Khong Dau Philips 4.5L</v>
       </c>
       <c r="D12" t="str">
-        <v>8710103856789</v>
+        <v>8710103856788</v>
       </c>
       <c r="E12" t="str">
         <v>1</v>
@@ -672,6 +705,9 @@
         <v>1.490.000</v>
       </c>
       <c r="G12" t="str">
+        <v>TikTok Shop</v>
+      </c>
+      <c r="H12" t="str">
         <v>Delivered</v>
       </c>
     </row>
@@ -686,7 +722,7 @@
         <v>Tai Nghe Xiaomi Redmi Buds 4</v>
       </c>
       <c r="D13" t="str">
-        <v>6934177785678</v>
+        <v>6934177785672</v>
       </c>
       <c r="E13" t="str">
         <v>2</v>
@@ -695,6 +731,9 @@
         <v>490.000</v>
       </c>
       <c r="G13" t="str">
+        <v>TikTok Shop</v>
+      </c>
+      <c r="H13" t="str">
         <v>Delivered</v>
       </c>
     </row>
@@ -709,7 +748,7 @@
         <v>Kem Chong Nang La Roche Posay</v>
       </c>
       <c r="D14" t="str">
-        <v>3337875591079</v>
+        <v>3337875591072</v>
       </c>
       <c r="E14" t="str">
         <v>1</v>
@@ -718,6 +757,9 @@
         <v>395.000</v>
       </c>
       <c r="G14" t="str">
+        <v>TikTok Shop</v>
+      </c>
+      <c r="H14" t="str">
         <v>Delivered</v>
       </c>
     </row>
@@ -732,7 +774,7 @@
         <v>Nuoc Tay Trang Cocoon Bi Dao 500ml</v>
       </c>
       <c r="D15" t="str">
-        <v>8936173200123</v>
+        <v>8936173200126</v>
       </c>
       <c r="E15" t="str">
         <v>1</v>
@@ -741,6 +783,9 @@
         <v>245.000</v>
       </c>
       <c r="G15" t="str">
+        <v>TikTok Shop</v>
+      </c>
+      <c r="H15" t="str">
         <v>Delivered</v>
       </c>
     </row>
@@ -755,7 +800,7 @@
         <v>Sua Rua Mat CeraVe 236ml</v>
       </c>
       <c r="D16" t="str">
-        <v>3337875597354</v>
+        <v>3337875597357</v>
       </c>
       <c r="E16" t="str">
         <v>1</v>
@@ -764,6 +809,9 @@
         <v>320.000</v>
       </c>
       <c r="G16" t="str">
+        <v>TikTok Shop</v>
+      </c>
+      <c r="H16" t="str">
         <v>Delivered</v>
       </c>
     </row>
@@ -778,7 +826,7 @@
         <v>Áo Khoác Gió Uniqlo</v>
       </c>
       <c r="D17" t="str">
-        <v>8935001234571</v>
+        <v>8935001234593</v>
       </c>
       <c r="E17" t="str">
         <v>1</v>
@@ -787,6 +835,9 @@
         <v>699.000</v>
       </c>
       <c r="G17" t="str">
+        <v>TikTok Shop</v>
+      </c>
+      <c r="H17" t="str">
         <v>Cancelled</v>
       </c>
     </row>
@@ -801,7 +852,7 @@
         <v>Dép Adidas Adilette Quai Ngang</v>
       </c>
       <c r="D18" t="str">
-        <v>8935001234575</v>
+        <v>8935001234623</v>
       </c>
       <c r="E18" t="str">
         <v>1</v>
@@ -810,6 +861,9 @@
         <v>750.000</v>
       </c>
       <c r="G18" t="str">
+        <v>TikTok Shop</v>
+      </c>
+      <c r="H18" t="str">
         <v>Refunded</v>
       </c>
     </row>
@@ -833,6 +887,9 @@
         <v>120.000</v>
       </c>
       <c r="G19" t="str">
+        <v>TikTok Shop</v>
+      </c>
+      <c r="H19" t="str">
         <v>Delivered</v>
       </c>
     </row>
@@ -847,7 +904,7 @@
         <v>Dây Sạc USB-C Anker 1m</v>
       </c>
       <c r="D20" t="str">
-        <v>B2B00123456</v>
+        <v>8935001999998</v>
       </c>
       <c r="E20" t="str">
         <v>2</v>
@@ -856,12 +913,15 @@
         <v>150.000</v>
       </c>
       <c r="G20" t="str">
+        <v>TikTok Shop</v>
+      </c>
+      <c r="H20" t="str">
         <v>Delivered</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H20"/>
   </ignoredErrors>
 </worksheet>
 </file>